--- a/patchr/resources/PLATES_v2.0.0/RB[BATCH_ID].xlsx
+++ b/patchr/resources/PLATES_v2.0.0/RB[BATCH_ID].xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpd0001/github/watch-wv/analysis/resources/PLATES_v2.0.0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpd0001/github/watch-wv/patchr/resources/PLATES_v2.0.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CAB94B4-4787-5E45-BA9D-58FFF9E9F75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57EB8B5-5DF5-5748-9B5A-4677976F03E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6460" yWindow="1580" windowWidth="23220" windowHeight="14800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>Date</t>
   </si>
@@ -92,13 +92,7 @@
     <t>Wall-E</t>
   </si>
   <si>
-    <t>Ceres Nanotrap Magnetic Virus Particles</t>
-  </si>
-  <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>Ceres Nanotrap Magnetic Microbiome B Particles</t>
   </si>
   <si>
     <t>Run By</t>
@@ -144,6 +138,15 @@
   </si>
   <si>
     <t>xxxxxxx</t>
+  </si>
+  <si>
+    <t>Ceres Nanotrap Microbiome A Particles</t>
+  </si>
+  <si>
+    <t>Ceres Nanotrap Microbiome B Particles</t>
+  </si>
+  <si>
+    <t>Ceres Nanotrap Microbiome A &amp; B Particles</t>
   </si>
 </sst>
 </file>
@@ -615,10 +618,10 @@
   <sheetData>
     <row r="1" spans="1:26" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="1"/>
@@ -647,7 +650,7 @@
     </row>
     <row r="2" spans="1:26" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>9</v>
@@ -711,7 +714,7 @@
     </row>
     <row r="4" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>14</v>
@@ -775,10 +778,10 @@
     </row>
     <row r="6" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -807,7 +810,7 @@
     </row>
     <row r="7" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="1"/>
@@ -904,7 +907,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -936,7 +939,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -965,10 +968,10 @@
     </row>
     <row r="12" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -28755,17 +28758,17 @@
           </x14:formula1>
           <xm:sqref>B5</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{54DC40FE-1531-CA42-8A84-F11C4FB254AD}">
+          <x14:formula1>
+            <xm:f>Lists!$C$2:$C$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>B12</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$10</xm:f>
           </x14:formula1>
           <xm:sqref>B10</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{54DC40FE-1531-CA42-8A84-F11C4FB254AD}">
-          <x14:formula1>
-            <xm:f>Lists!$C$2:$C$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>B12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -34010,7 +34013,7 @@
         <v>7</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -34018,10 +34021,10 @@
         <v>15</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -34029,34 +34032,37 @@
         <v>16</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C3" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="19" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -35054,6 +35060,7 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
